--- a/public/GPS_PLANTILLA.xlsx
+++ b/public/GPS_PLANTILLA.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,38 +27,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C6F135"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color rgb="00EEEEEE"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C6F135"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <color rgb="00EEEEEE"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00C6F135"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <color rgb="00AAAAAA"/>
       <sz val="10"/>
     </font>
@@ -117,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -137,17 +128,16 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -707,14 +697,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00C6F135"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -723,155 +712,134 @@
           <t>INSTRUCCIONES DE USO</t>
         </is>
       </c>
-      <c r="B1" s="7" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="8" t="inlineStr"/>
-      <c r="B2" s="7" t="n"/>
+      <c r="A2" s="7" t="inlineStr"/>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>1. Completá los datos en la hoja 'GPS_DATOS'</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="n"/>
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>1. Completá los datos en la hoja GPS_DATOS</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>2. La primera columna debe ser el nombre completo del jugador</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>2. La primera columna debe ser el nombre completo del jugador (igual al sistema)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>3. No modifiques los nombres de las columnas</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>4. Podés agregar o quitar filas de jugadores según necesites</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>5. Guardá el archivo como .xlsx y subilo en la sección GPS</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="8" t="inlineStr"/>
-      <c r="B8" s="7" t="n"/>
+      <c r="A8" s="7" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>DESCRIPCIÓN DE COLUMNAS:</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>COLUMNAS:</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="8" t="inlineStr"/>
-      <c r="B10" s="7" t="n"/>
+      <c r="A10" s="7" t="inlineStr"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>Nombre y Apellido     → Nombre completo del jugador (debe coincidir con el sistema)</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n"/>
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Nombre y Apellido     → Nombre completo del jugador</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Tiempo (min)          → Minutos jugados/entrenados</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Tot Dist (m)          → Distancia total recorrida en metros</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n"/>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Tot Dist (m)          → Distancia total en metros</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Meterage Per Minute   → Metros por minuto (intensidad)</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Vel B4 Tot Dist (m)   → Distancia a alta velocidad (15-20 km/h)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>High Speed Dist (m)   → Distancia a muy alta velocidad (HSR)</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Vel B6 Tot Dist (m)   → Distancia en sprint (&gt;20 km/h)</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Número Sprint         → Cantidad de sprints realizados</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>Acc B2-3 Tot Effs     → Aceleraciones &gt;3 m/s² (ACE &gt;3)</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n"/>
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Acc B2-3 Tot Effs     → Aceleraciones &gt;3 m/s2 (ACE &gt;3)</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>Decel B2-3 Tot Effs   → Desaceleraciones &gt;3 m/s² (DEC &gt;3)</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="n"/>
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Decel B2-3 Tot Effs   → Desaceleraciones &gt;3 m/s2 (DEC &gt;3)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>Velocidad Máxima      → Velocidad máxima alcanzada en km/h</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="n"/>
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Velocidad Maxima      → Velocidad maxima alcanzada en km/h</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
